--- a/assets/Consultoria/Información de referencia/Estadista IIEE Estudiantes RER FyA 2024 y 2025/Identificador_Servicios Educativos FyA RER 2025 (3).xlsx
+++ b/assets/Consultoria/Información de referencia/Estadista IIEE Estudiantes RER FyA 2024 y 2025/Identificador_Servicios Educativos FyA RER 2025 (3).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gtuse\Desktop\DATA Estadística 2025\Ratificada x RER 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Proyectos\Reasis\assets\Consultoria\Información de referencia\Estadista IIEE Estudiantes RER FyA 2024 y 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AA6C2B9-C91A-4E57-9EB1-1D51387B9B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AE4D39-1B53-4274-A708-32973E5B0675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="437" firstSheet="1" activeTab="1" xr2:uid="{92E76F33-8CBB-4579-B552-98DB9C381C60}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="437" firstSheet="1" activeTab="1" xr2:uid="{92E76F33-8CBB-4579-B552-98DB9C381C60}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" state="veryHidden" r:id="rId1"/>
@@ -1336,16 +1336,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{340B5293-1A3C-4472-A1FD-1252AA4654B1}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:E386"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.3984375" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" customWidth="1"/>
-    <col min="3" max="3" width="12.296875" customWidth="1"/>
-    <col min="4" max="4" width="13.296875" customWidth="1"/>
-    <col min="5" max="5" width="32.296875" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>108</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1208214</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>204974</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>580514</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>1678861</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>219808</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>1376268</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>227900</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>1505494</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>1527373</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>740365</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>495762</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>721647</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>437525</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>721639</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>420406</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>1200906</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>775320</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>359059</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>1194695</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>1335637</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>775379</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>290346</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>437541</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>1116854</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>1151331</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>682211</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>1221498</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>830885</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>1625938</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>577098</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>836791</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>689927</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>1370725</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>657122</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>1383363</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>487140</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>1715424</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>398347</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>937813</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>595082</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>273359</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>410266</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>1367366</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>421594</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>541201</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>561084</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>1538453</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>1207166</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>1626001</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>666677</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>896001</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>1152321</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>1598861</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>1584150</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>1568799</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>1791433</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>410100</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>1682285</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>437509</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>520221</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>1241926</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>1329580</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>1737394</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>738203</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>272773</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>1335710</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>1105329</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>676734</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>271551</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>272567</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>693663</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>347161</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>275107</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>582932</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>1324193</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>301408</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>686741</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>1335702</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>1715820</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>336891</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>658427</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>420562</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>601781</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>1085646</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>1332659</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>651398</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>1681212</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>933937</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>687194</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>1261775</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>571562</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>409672</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>633040</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>481820</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>263111</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>410225</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>1335728</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>1795038</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>1527399</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>1393628</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>1378355</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>1772672</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>415117</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>674895</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>229799</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>1324201</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>1374834</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>535724</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>626424</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>398313</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>420380</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>1530971</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>1191808</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>1154608</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>1236397</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>493338</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>239905</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>1060755</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>428920</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>433029</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>1194778</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>1133545</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>435446</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>436204</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>1366632</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>733535</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>738419</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>437533</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>1735802</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>464610</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>820779</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>409797</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>665455</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>775296</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>807156</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>683466</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>1062470</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>510404</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>513465</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>236786</v>
       </c>
@@ -3742,7 +3742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>519793</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>1715416</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>1506823</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>535104</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>1153964</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>1084474</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>1447499</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>541219</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>737783</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>552661</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>1791466</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>571232</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>1401124</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>879791</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>410233</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>411512</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>592428</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>1625904</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>1376318</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>236778</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>1315084</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>235341</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>1393610</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>262998</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>1444223</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>1511849</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>600692</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>1745710</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>1529833</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>613547</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>1529718</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>1275577</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>1376854</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>263053</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>1795046</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>1553726</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>1785138</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>1457605</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>664706</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>414987</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>855791</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>1152057</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>496877</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>1194737</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>386755</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>1385103</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>1368844</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>1402692</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>350447</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>1376300</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>1527381</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>600932</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>1781962</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>1495167</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>433011</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>933960</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>1705029</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>224634</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>355289</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>691311</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>1516277</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>733600</v>
       </c>
@@ -4796,7 +4796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>1608132</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>1151661</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>617183</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>738427</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>1516269</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>1527365</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>271379</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>1210491</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>435370</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>767350</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>1154368</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>428771</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>1268150</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>1636455</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>1367341</v>
       </c>
@@ -5051,7 +5051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>1639145</v>
       </c>
@@ -5068,7 +5068,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>2732724</v>
       </c>
@@ -5082,7 +5082,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>595108</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>686386</v>
       </c>
@@ -5116,7 +5116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>1236967</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>583021</v>
       </c>
@@ -5150,7 +5150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>1343813</v>
       </c>
@@ -5167,7 +5167,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>1785484</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>1425875</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>1504026</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>592543</v>
       </c>
@@ -5235,7 +5235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>415141</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>838455</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>3916573</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>1147735</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>235333</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>1457365</v>
       </c>
@@ -5331,7 +5331,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>1551944</v>
       </c>
@@ -5348,7 +5348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>1148402</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>323873</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>354472</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>329326</v>
       </c>
@@ -5416,7 +5416,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>673780</v>
       </c>
@@ -5433,7 +5433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>613943</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>577478</v>
       </c>
@@ -5467,7 +5467,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>424770</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>901918</v>
       </c>
@@ -5501,7 +5501,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>938142</v>
       </c>
@@ -5518,7 +5518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>323865</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>519348</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>1393578</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>1060276</v>
       </c>
@@ -5586,7 +5586,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>1678879</v>
       </c>
@@ -5603,7 +5603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>1062058</v>
       </c>
@@ -5620,7 +5620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>1378702</v>
       </c>
@@ -5637,7 +5637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>683474</v>
       </c>
@@ -5654,7 +5654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>1381862</v>
       </c>
@@ -5671,7 +5671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>1153162</v>
       </c>
@@ -5688,7 +5688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>1613371</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>701284</v>
       </c>
@@ -5722,7 +5722,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>1268119</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>938118</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>1547231</v>
       </c>
@@ -5773,7 +5773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>1116896</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>1130012</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>1393594</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>530535</v>
       </c>
@@ -5841,7 +5841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>579987</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>1785476</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>355271</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>1715440</v>
       </c>
@@ -5909,7 +5909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>663377</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>757872</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>1538461</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>1741123</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>1527340</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>693374</v>
       </c>
@@ -6011,7 +6011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>578450</v>
       </c>
@@ -6028,7 +6028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>1735729</v>
       </c>
@@ -6045,7 +6045,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>1411255</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>260315</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>1041631</v>
       </c>
@@ -6096,7 +6096,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>398370</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>840504</v>
       </c>
@@ -6130,7 +6130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>1370709</v>
       </c>
@@ -6147,7 +6147,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>916023</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>1186451</v>
       </c>
@@ -6181,7 +6181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>693382</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>1788264</v>
       </c>
@@ -6215,7 +6215,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>1745728</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>1151695</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>1335744</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>1393602</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>1197987</v>
       </c>
@@ -6300,7 +6300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>1210137</v>
       </c>
@@ -6317,7 +6317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>715011</v>
       </c>
@@ -6334,7 +6334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>409706</v>
       </c>
@@ -6351,7 +6351,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>402248</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>636704</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>359323</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>1257245</v>
       </c>
@@ -6419,7 +6419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>1261189</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>1385095</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>737791</v>
       </c>
@@ -6470,7 +6470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>1236686</v>
       </c>
@@ -6487,7 +6487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>1263219</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>1563212</v>
       </c>
@@ -6521,7 +6521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>1104801</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>1152255</v>
       </c>
@@ -6555,7 +6555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>1714211</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>1229434</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>437517</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>571356</v>
       </c>
@@ -6623,7 +6623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>1155530</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>1265768</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>433037</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>762880</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>1262856</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>1154129</v>
       </c>
@@ -6725,7 +6725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>1370717</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>761585</v>
       </c>
@@ -6759,7 +6759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>1529825</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>1276120</v>
       </c>
@@ -6793,7 +6793,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>876441</v>
       </c>
@@ -6810,7 +6810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>204933</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>535195</v>
       </c>
@@ -6844,7 +6844,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>1276674</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>290809</v>
       </c>
@@ -6878,7 +6878,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>1070630</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>334995</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>410316</v>
       </c>
@@ -6929,7 +6929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>428714</v>
       </c>
@@ -6946,7 +6946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>359042</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>818682</v>
       </c>
@@ -6980,7 +6980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>1324185</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>1273960</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>205716</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>464628</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>205401</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>1153881</v>
       </c>
@@ -7082,7 +7082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>1419977</v>
       </c>
@@ -7099,7 +7099,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>415059</v>
       </c>
@@ -7116,7 +7116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>900647</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>495234</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>1072297</v>
       </c>
@@ -7167,7 +7167,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>420430</v>
       </c>
@@ -7184,7 +7184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>1151414</v>
       </c>
@@ -7201,7 +7201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>1261577</v>
       </c>
@@ -7218,7 +7218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>3891735</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>1389972</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>308445</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>1393586</v>
       </c>
@@ -7283,7 +7283,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>1210095</v>
       </c>
@@ -7300,7 +7300,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>577841</v>
       </c>
@@ -7317,7 +7317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>1320001</v>
       </c>
@@ -7334,7 +7334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>3893301</v>
       </c>
@@ -7348,7 +7348,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A355">
         <v>1396258</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>1153527</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>761668</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>714410</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>410118</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>1250323</v>
       </c>
@@ -7450,7 +7450,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>350496</v>
       </c>
@@ -7467,7 +7467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>1433515</v>
       </c>
@@ -7484,7 +7484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A363">
         <v>840595</v>
       </c>
@@ -7501,7 +7501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A364">
         <v>420448</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A365">
         <v>778076</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A366">
         <v>410258</v>
       </c>
@@ -7552,7 +7552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A367">
         <v>1448596</v>
       </c>
@@ -7569,7 +7569,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A368">
         <v>1364264</v>
       </c>
@@ -7586,7 +7586,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A369">
         <v>433045</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A370">
         <v>1385079</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A371">
         <v>762500</v>
       </c>
@@ -7637,7 +7637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A372">
         <v>571745</v>
       </c>
@@ -7654,7 +7654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A373">
         <v>1633189</v>
       </c>
@@ -7671,7 +7671,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A374">
         <v>1402866</v>
       </c>
@@ -7688,7 +7688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A375">
         <v>1192921</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A376">
         <v>1306182</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A377">
         <v>664763</v>
       </c>
@@ -7739,7 +7739,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A378">
         <v>1397348</v>
       </c>
@@ -7756,7 +7756,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A379">
         <v>1527233</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A380">
         <v>1367358</v>
       </c>
@@ -7790,7 +7790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A381">
         <v>1625987</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A382">
         <v>843326</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A383">
         <v>1448588</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A384">
         <v>1154400</v>
       </c>
@@ -7858,7 +7858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A385">
         <v>1329788</v>
       </c>
@@ -7875,7 +7875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A386">
         <v>260307</v>
       </c>
@@ -7904,18 +7904,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{183AFE64-522F-4AF3-8495-058041DE8C57}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:J380"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.69921875" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" customWidth="1"/>
-    <col min="3" max="3" width="11.796875" customWidth="1"/>
-    <col min="4" max="4" width="11.8984375" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.2109375" customWidth="1"/>
+    <col min="3" max="3" width="11.78515625" customWidth="1"/>
+    <col min="4" max="4" width="11.92578125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="25.8984375" customWidth="1"/>
-    <col min="9" max="9" width="85.8984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.92578125" customWidth="1"/>
+    <col min="9" max="9" width="85.92578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="37" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>108</v>
       </c>
@@ -7944,7 +7944,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>1208214</v>
       </c>
@@ -7964,7 +7964,7 @@
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>409797</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>580514</v>
       </c>
@@ -8010,7 +8010,7 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>410118</v>
       </c>
@@ -8036,7 +8036,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>219808</v>
       </c>
@@ -8056,7 +8056,7 @@
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>410316</v>
       </c>
@@ -8082,7 +8082,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>227900</v>
       </c>
@@ -8102,7 +8102,7 @@
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>1505494</v>
       </c>
@@ -8122,7 +8122,7 @@
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>1062058</v>
       </c>
@@ -8148,7 +8148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>409706</v>
       </c>
@@ -8174,7 +8174,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>495762</v>
       </c>
@@ -8194,7 +8194,7 @@
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>410100</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>437525</v>
       </c>
@@ -8240,7 +8240,7 @@
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>204933</v>
       </c>
@@ -8266,7 +8266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>519793</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>1200906</v>
       </c>
@@ -8312,7 +8312,7 @@
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>775320</v>
       </c>
@@ -8332,7 +8332,7 @@
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>359059</v>
       </c>
@@ -8352,7 +8352,7 @@
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>1194695</v>
       </c>
@@ -8372,7 +8372,7 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>1335637</v>
       </c>
@@ -8392,7 +8392,7 @@
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>290346</v>
       </c>
@@ -8412,7 +8412,7 @@
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>437541</v>
       </c>
@@ -8432,7 +8432,7 @@
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>1116854</v>
       </c>
@@ -8452,7 +8452,7 @@
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>592428</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>205716</v>
       </c>
@@ -8504,7 +8504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>1221498</v>
       </c>
@@ -8524,7 +8524,7 @@
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>409672</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>410225</v>
       </c>
@@ -8576,7 +8576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>577098</v>
       </c>
@@ -8596,7 +8596,7 @@
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>836791</v>
       </c>
@@ -8616,7 +8616,7 @@
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>689927</v>
       </c>
@@ -8636,7 +8636,7 @@
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>1370725</v>
       </c>
@@ -8656,7 +8656,7 @@
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>410233</v>
       </c>
@@ -8682,7 +8682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>1383363</v>
       </c>
@@ -8702,7 +8702,7 @@
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>410258</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>410266</v>
       </c>
@@ -8754,7 +8754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>204974</v>
       </c>
@@ -8780,7 +8780,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>205401</v>
       </c>
@@ -8806,7 +8806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>487140</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>592543</v>
       </c>
@@ -8858,7 +8858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <v>1343813</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <v>1367366</v>
       </c>
@@ -8904,7 +8904,7 @@
       <c r="G43" s="10"/>
       <c r="H43" s="10"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <v>1772672</v>
       </c>
@@ -8930,7 +8930,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <v>1457605</v>
       </c>
@@ -8956,7 +8956,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <v>1636455</v>
       </c>
@@ -8982,7 +8982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
         <v>1538453</v>
       </c>
@@ -9002,7 +9002,7 @@
       <c r="G47" s="10"/>
       <c r="H47" s="10"/>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
         <v>1207166</v>
       </c>
@@ -9022,7 +9022,7 @@
       <c r="G48" s="10"/>
       <c r="H48" s="10"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" s="1">
         <v>1741123</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" s="1">
         <v>1457365</v>
       </c>
@@ -9074,7 +9074,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="1">
         <v>1527373</v>
       </c>
@@ -9100,7 +9100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" s="1">
         <v>1598861</v>
       </c>
@@ -9120,7 +9120,7 @@
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="1">
         <v>721647</v>
       </c>
@@ -9146,7 +9146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" s="1">
         <v>721639</v>
       </c>
@@ -9172,7 +9172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" s="1">
         <v>1151331</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56" s="1">
         <v>437509</v>
       </c>
@@ -9218,7 +9218,7 @@
       <c r="G56" s="10"/>
       <c r="H56" s="10"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" s="1">
         <v>682211</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" s="1">
         <v>1241926</v>
       </c>
@@ -9264,7 +9264,7 @@
       <c r="G58" s="10"/>
       <c r="H58" s="10"/>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59" s="1">
         <v>1329580</v>
       </c>
@@ -9284,7 +9284,7 @@
       <c r="G59" s="10"/>
       <c r="H59" s="10"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" s="1">
         <v>398347</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" s="1">
         <v>1152321</v>
       </c>
@@ -9336,7 +9336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
         <v>1335710</v>
       </c>
@@ -9356,7 +9356,7 @@
       <c r="G62" s="10"/>
       <c r="H62" s="10"/>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63" s="1">
         <v>1105329</v>
       </c>
@@ -9376,7 +9376,7 @@
       <c r="G63" s="10"/>
       <c r="H63" s="10"/>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64" s="1">
         <v>676734</v>
       </c>
@@ -9396,7 +9396,7 @@
       <c r="G64" s="10"/>
       <c r="H64" s="10"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" s="1">
         <v>1682285</v>
       </c>
@@ -9422,7 +9422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" s="1">
         <v>738203</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67" s="1">
         <v>693663</v>
       </c>
@@ -9468,7 +9468,7 @@
       <c r="G67" s="10"/>
       <c r="H67" s="10"/>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
         <v>347161</v>
       </c>
@@ -9488,7 +9488,7 @@
       <c r="G68" s="10"/>
       <c r="H68" s="10"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" s="1">
         <v>651398</v>
       </c>
@@ -9514,7 +9514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70" s="1">
         <v>582932</v>
       </c>
@@ -9534,7 +9534,7 @@
       <c r="G70" s="10"/>
       <c r="H70" s="10"/>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71" s="1">
         <v>1324193</v>
       </c>
@@ -9554,7 +9554,7 @@
       <c r="G71" s="10"/>
       <c r="H71" s="10"/>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72" s="1">
         <v>301408</v>
       </c>
@@ -9574,7 +9574,7 @@
       <c r="G72" s="10"/>
       <c r="H72" s="10"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="1">
         <v>1261775</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
         <v>1335702</v>
       </c>
@@ -9620,7 +9620,7 @@
       <c r="G74" s="10"/>
       <c r="H74" s="10"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" s="1">
         <v>1527399</v>
       </c>
@@ -9646,7 +9646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76" s="1">
         <v>336891</v>
       </c>
@@ -9666,7 +9666,7 @@
       <c r="G76" s="10"/>
       <c r="H76" s="10"/>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A77" s="1">
         <v>658427</v>
       </c>
@@ -9686,7 +9686,7 @@
       <c r="G77" s="10"/>
       <c r="H77" s="10"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" s="1">
         <v>1378355</v>
       </c>
@@ -9712,7 +9712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" s="1">
         <v>601781</v>
       </c>
@@ -9732,7 +9732,7 @@
       <c r="G79" s="10"/>
       <c r="H79" s="10"/>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" s="1">
         <v>1085646</v>
       </c>
@@ -9752,7 +9752,7 @@
       <c r="G80" s="10"/>
       <c r="H80" s="10"/>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" s="1">
         <v>1332659</v>
       </c>
@@ -9772,7 +9772,7 @@
       <c r="G81" s="10"/>
       <c r="H81" s="10"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="1">
         <v>398313</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83" s="1">
         <v>1154608</v>
       </c>
@@ -9824,7 +9824,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" s="1">
         <v>933937</v>
       </c>
@@ -9844,7 +9844,7 @@
       <c r="G84" s="10"/>
       <c r="H84" s="10"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" s="1">
         <v>738419</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86" s="1">
         <v>683466</v>
       </c>
@@ -9896,7 +9896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87" s="1">
         <v>571562</v>
       </c>
@@ -9916,7 +9916,7 @@
       <c r="G87" s="10"/>
       <c r="H87" s="10"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" s="1">
         <v>1153964</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A89" s="1">
         <v>1152057</v>
       </c>
@@ -9968,7 +9968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" s="1">
         <v>481820</v>
       </c>
@@ -9988,7 +9988,7 @@
       <c r="G90" s="10"/>
       <c r="H90" s="10"/>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" s="1">
         <v>263111</v>
       </c>
@@ -10008,7 +10008,7 @@
       <c r="G91" s="10"/>
       <c r="H91" s="10"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" s="1">
         <v>1527381</v>
       </c>
@@ -10034,7 +10034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93" s="1">
         <v>1335728</v>
       </c>
@@ -10054,7 +10054,7 @@
       <c r="G93" s="10"/>
       <c r="H93" s="10"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" s="1">
         <v>738427</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" s="1">
         <v>1393628</v>
       </c>
@@ -10100,7 +10100,7 @@
       <c r="G95" s="10"/>
       <c r="H95" s="10"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" s="1">
         <v>1527365</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" s="1">
         <v>1210491</v>
       </c>
@@ -10152,7 +10152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="1">
         <v>1154368</v>
       </c>
@@ -10178,7 +10178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="1">
         <v>1147735</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A100" s="1">
         <v>229799</v>
       </c>
@@ -10224,7 +10224,7 @@
       <c r="G100" s="10"/>
       <c r="H100" s="10"/>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" s="1">
         <v>1324201</v>
       </c>
@@ -10244,7 +10244,7 @@
       <c r="G101" s="10"/>
       <c r="H101" s="10"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102" s="1">
         <v>1148402</v>
       </c>
@@ -10270,7 +10270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A103" s="1">
         <v>535724</v>
       </c>
@@ -10290,7 +10290,7 @@
       <c r="G103" s="10"/>
       <c r="H103" s="10"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" s="1">
         <v>683474</v>
       </c>
@@ -10316,7 +10316,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" s="1">
         <v>1527340</v>
       </c>
@@ -10342,7 +10342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" s="1">
         <v>398370</v>
       </c>
@@ -10368,7 +10368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" s="1">
         <v>1151695</v>
       </c>
@@ -10394,7 +10394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" s="1">
         <v>1263219</v>
       </c>
@@ -10420,7 +10420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109" s="1">
         <v>493338</v>
       </c>
@@ -10440,7 +10440,7 @@
       <c r="G109" s="10"/>
       <c r="H109" s="10"/>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A110" s="1">
         <v>239905</v>
       </c>
@@ -10460,7 +10460,7 @@
       <c r="G110" s="10"/>
       <c r="H110" s="10"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" s="1">
         <v>1563212</v>
       </c>
@@ -10486,7 +10486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" s="1">
         <v>433029</v>
       </c>
@@ -10506,7 +10506,7 @@
       <c r="G112" s="10"/>
       <c r="H112" s="10"/>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113" s="1">
         <v>1194778</v>
       </c>
@@ -10526,7 +10526,7 @@
       <c r="G113" s="10"/>
       <c r="H113" s="10"/>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114" s="1">
         <v>435446</v>
       </c>
@@ -10546,7 +10546,7 @@
       <c r="G114" s="10"/>
       <c r="H114" s="10"/>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A115" s="1">
         <v>436204</v>
       </c>
@@ -10566,7 +10566,7 @@
       <c r="G115" s="10"/>
       <c r="H115" s="10"/>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A116" s="1">
         <v>1366632</v>
       </c>
@@ -10586,7 +10586,7 @@
       <c r="G116" s="10"/>
       <c r="H116" s="10"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="1">
         <v>1152255</v>
       </c>
@@ -10612,7 +10612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" s="1">
         <v>1262856</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A119" s="1">
         <v>437533</v>
       </c>
@@ -10658,7 +10658,7 @@
       <c r="G119" s="10"/>
       <c r="H119" s="10"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="1">
         <v>1154129</v>
       </c>
@@ -10684,7 +10684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A121" s="1">
         <v>820779</v>
       </c>
@@ -10704,7 +10704,7 @@
       <c r="G121" s="10"/>
       <c r="H121" s="10"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="1">
         <v>1273960</v>
       </c>
@@ -10730,7 +10730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A123" s="1">
         <v>665455</v>
       </c>
@@ -10750,7 +10750,7 @@
       <c r="G123" s="10"/>
       <c r="H123" s="10"/>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A124" s="1">
         <v>775296</v>
       </c>
@@ -10770,7 +10770,7 @@
       <c r="G124" s="10"/>
       <c r="H124" s="10"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="1">
         <v>1153881</v>
       </c>
@@ -10796,7 +10796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" s="1">
         <v>1151414</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A127" s="1">
         <v>1062470</v>
       </c>
@@ -10842,7 +10842,7 @@
       <c r="G127" s="10"/>
       <c r="H127" s="10"/>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A128" s="1">
         <v>510404</v>
       </c>
@@ -10862,7 +10862,7 @@
       <c r="G128" s="10"/>
       <c r="H128" s="10"/>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A129" s="1">
         <v>513465</v>
       </c>
@@ -10882,7 +10882,7 @@
       <c r="G129" s="10"/>
       <c r="H129" s="10"/>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A130" s="1">
         <v>236786</v>
       </c>
@@ -10902,7 +10902,7 @@
       <c r="G130" s="10"/>
       <c r="H130" s="10"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A131" s="1">
         <v>1261577</v>
       </c>
@@ -10928,7 +10928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A132" s="1">
         <v>1320001</v>
       </c>
@@ -10954,7 +10954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A133" s="1">
         <v>1506823</v>
       </c>
@@ -10974,7 +10974,7 @@
       <c r="G133" s="10"/>
       <c r="H133" s="10"/>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A134" s="1">
         <v>535104</v>
       </c>
@@ -10994,7 +10994,7 @@
       <c r="G134" s="10"/>
       <c r="H134" s="10"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A135" s="1">
         <v>1153527</v>
       </c>
@@ -11020,7 +11020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A136" s="1">
         <v>1084474</v>
       </c>
@@ -11040,7 +11040,7 @@
       <c r="G136" s="10"/>
       <c r="H136" s="10"/>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A137" s="1">
         <v>1447499</v>
       </c>
@@ -11060,7 +11060,7 @@
       <c r="G137" s="10"/>
       <c r="H137" s="10"/>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A138" s="1">
         <v>541219</v>
       </c>
@@ -11080,7 +11080,7 @@
       <c r="G138" s="10"/>
       <c r="H138" s="10"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139" s="1">
         <v>1306182</v>
       </c>
@@ -11106,7 +11106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A140" s="1">
         <v>1527233</v>
       </c>
@@ -11132,7 +11132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A141" s="1">
         <v>1154400</v>
       </c>
@@ -11158,7 +11158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A142" s="1">
         <v>1401124</v>
       </c>
@@ -11178,7 +11178,7 @@
       <c r="G142" s="10"/>
       <c r="H142" s="10"/>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A143" s="1">
         <v>879791</v>
       </c>
@@ -11198,7 +11198,7 @@
       <c r="G143" s="10"/>
       <c r="H143" s="10"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A144" s="1">
         <v>571232</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A145" s="1">
         <v>411512</v>
       </c>
@@ -11247,7 +11247,7 @@
       <c r="G145" s="10"/>
       <c r="H145" s="10"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146" s="1">
         <v>737783</v>
       </c>
@@ -11276,7 +11276,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A147" s="1">
         <v>737791</v>
       </c>
@@ -11305,7 +11305,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A148" s="1">
         <v>937813</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A149" s="1">
         <v>236778</v>
       </c>
@@ -11354,7 +11354,7 @@
       <c r="G149" s="10"/>
       <c r="H149" s="10"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A150" s="1">
         <v>938118</v>
       </c>
@@ -11383,7 +11383,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A151" s="1">
         <v>235341</v>
       </c>
@@ -11403,7 +11403,7 @@
       <c r="G151" s="10"/>
       <c r="H151" s="10"/>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152" s="1">
         <v>1393610</v>
       </c>
@@ -11423,7 +11423,7 @@
       <c r="G152" s="10"/>
       <c r="H152" s="10"/>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A153" s="1">
         <v>262998</v>
       </c>
@@ -11443,7 +11443,7 @@
       <c r="G153" s="10"/>
       <c r="H153" s="10"/>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A154" s="1">
         <v>1444223</v>
       </c>
@@ -11463,7 +11463,7 @@
       <c r="G154" s="10"/>
       <c r="H154" s="10"/>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A155" s="1">
         <v>1511849</v>
       </c>
@@ -11483,7 +11483,7 @@
       <c r="G155" s="10"/>
       <c r="H155" s="10"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A156" s="1">
         <v>938142</v>
       </c>
@@ -11512,7 +11512,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A157" s="1">
         <v>674895</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A158" s="1">
         <v>613547</v>
       </c>
@@ -11561,7 +11561,7 @@
       <c r="G158" s="10"/>
       <c r="H158" s="10"/>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A159" s="1">
         <v>1529718</v>
       </c>
@@ -11581,7 +11581,7 @@
       <c r="G159" s="10"/>
       <c r="H159" s="10"/>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A160" s="1">
         <v>1275577</v>
       </c>
@@ -11601,7 +11601,7 @@
       <c r="G160" s="10"/>
       <c r="H160" s="10"/>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A161" s="1">
         <v>1376854</v>
       </c>
@@ -11621,7 +11621,7 @@
       <c r="G161" s="10"/>
       <c r="H161" s="10"/>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A162" s="1">
         <v>263053</v>
       </c>
@@ -11641,7 +11641,7 @@
       <c r="G162" s="10"/>
       <c r="H162" s="10"/>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A163" s="1">
         <v>1553726</v>
       </c>
@@ -11661,7 +11661,7 @@
       <c r="G163" s="10"/>
       <c r="H163" s="10"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A164" s="1">
         <v>260307</v>
       </c>
@@ -11690,7 +11690,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A165" s="1">
         <v>916023</v>
       </c>
@@ -11719,7 +11719,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A166" s="1">
         <v>664706</v>
       </c>
@@ -11739,7 +11739,7 @@
       <c r="G166" s="10"/>
       <c r="H166" s="10"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A167" s="1">
         <v>1785476</v>
       </c>
@@ -11768,7 +11768,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A168" s="1">
         <v>350447</v>
       </c>
@@ -11797,7 +11797,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A169" s="1">
         <v>855791</v>
       </c>
@@ -11817,7 +11817,7 @@
       <c r="G169" s="10"/>
       <c r="H169" s="10"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A170" s="1">
         <v>260315</v>
       </c>
@@ -11846,7 +11846,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A171" s="1">
         <v>496877</v>
       </c>
@@ -11866,7 +11866,7 @@
       <c r="G171" s="10"/>
       <c r="H171" s="10"/>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A172" s="1">
         <v>1194737</v>
       </c>
@@ -11886,7 +11886,7 @@
       <c r="G172" s="10"/>
       <c r="H172" s="10"/>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A173" s="1">
         <v>386755</v>
       </c>
@@ -11906,7 +11906,7 @@
       <c r="G173" s="10"/>
       <c r="H173" s="10"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A174" s="1">
         <v>1715820</v>
       </c>
@@ -11935,7 +11935,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A175" s="1">
         <v>571745</v>
       </c>
@@ -11964,7 +11964,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A176" s="1">
         <v>571356</v>
       </c>
@@ -11993,7 +11993,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A177" s="1">
         <v>350496</v>
       </c>
@@ -12022,7 +12022,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A178" s="1">
         <v>613943</v>
       </c>
@@ -12051,7 +12051,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A179" s="1">
         <v>1781962</v>
       </c>
@@ -12071,7 +12071,7 @@
       <c r="G179" s="10"/>
       <c r="H179" s="10"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A180" s="1">
         <v>464610</v>
       </c>
@@ -12100,7 +12100,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A181" s="1">
         <v>433011</v>
       </c>
@@ -12120,7 +12120,7 @@
       <c r="G181" s="10"/>
       <c r="H181" s="10"/>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A182" s="1">
         <v>933960</v>
       </c>
@@ -12140,7 +12140,7 @@
       <c r="G182" s="10"/>
       <c r="H182" s="10"/>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A183" s="1">
         <v>1705029</v>
       </c>
@@ -12160,7 +12160,7 @@
       <c r="G183" s="10"/>
       <c r="H183" s="10"/>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A184" s="1">
         <v>224634</v>
       </c>
@@ -12180,7 +12180,7 @@
       <c r="G184" s="10"/>
       <c r="H184" s="10"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A185" s="1">
         <v>464628</v>
       </c>
@@ -12209,7 +12209,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A186" s="1">
         <v>691311</v>
       </c>
@@ -12229,7 +12229,7 @@
       <c r="G186" s="10"/>
       <c r="H186" s="10"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A187" s="1">
         <v>355271</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A188" s="1">
         <v>552661</v>
       </c>
@@ -12287,7 +12287,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A189" s="1">
         <v>561084</v>
       </c>
@@ -12316,7 +12316,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A190" s="1">
         <v>1151661</v>
       </c>
@@ -12336,7 +12336,7 @@
       <c r="G190" s="10"/>
       <c r="H190" s="10"/>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A191" s="1">
         <v>617183</v>
       </c>
@@ -12356,7 +12356,7 @@
       <c r="G191" s="10"/>
       <c r="H191" s="10"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A192" s="1">
         <v>355289</v>
       </c>
@@ -12385,7 +12385,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A193" s="1">
         <v>673780</v>
       </c>
@@ -12414,7 +12414,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A194" s="1">
         <v>840595</v>
       </c>
@@ -12443,7 +12443,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A195" s="1">
         <v>840504</v>
       </c>
@@ -12472,7 +12472,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A196" s="1">
         <v>626424</v>
       </c>
@@ -12501,7 +12501,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A197" s="1">
         <v>767350</v>
       </c>
@@ -12521,7 +12521,7 @@
       <c r="G197" s="10"/>
       <c r="H197" s="10"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A198" s="1">
         <v>1516269</v>
       </c>
@@ -12550,7 +12550,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A199" s="1">
         <v>1516277</v>
       </c>
@@ -12579,7 +12579,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A200" s="1">
         <v>1268150</v>
       </c>
@@ -12599,7 +12599,7 @@
       <c r="G200" s="10"/>
       <c r="H200" s="10"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A201" s="1">
         <v>1681212</v>
       </c>
@@ -12628,7 +12628,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A202" s="1">
         <v>1367341</v>
       </c>
@@ -12648,7 +12648,7 @@
       <c r="G202" s="10"/>
       <c r="H202" s="10"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A203" s="1">
         <v>1236397</v>
       </c>
@@ -12677,7 +12677,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A204" s="1">
         <v>1715416</v>
       </c>
@@ -12706,7 +12706,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A205" s="1">
         <v>1715424</v>
       </c>
@@ -12735,7 +12735,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A206" s="1">
         <v>583021</v>
       </c>
@@ -12755,7 +12755,7 @@
       <c r="G206" s="10"/>
       <c r="H206" s="10"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A207" s="1">
         <v>1715440</v>
       </c>
@@ -12784,7 +12784,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A208" s="1">
         <v>1425875</v>
       </c>
@@ -12804,7 +12804,7 @@
       <c r="G208" s="10"/>
       <c r="H208" s="10"/>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A209" s="1">
         <v>1504026</v>
       </c>
@@ -12824,7 +12824,7 @@
       <c r="G209" s="10"/>
       <c r="H209" s="10"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A210" s="1">
         <v>1745710</v>
       </c>
@@ -12853,7 +12853,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A211" s="1">
         <v>1745728</v>
       </c>
@@ -12882,7 +12882,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A212" s="1">
         <v>3916573</v>
       </c>
@@ -12907,7 +12907,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A213" s="1">
         <v>3893301</v>
       </c>
@@ -12934,7 +12934,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A214" s="1">
         <v>3891735</v>
       </c>
@@ -12961,7 +12961,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A215" s="1">
         <v>235333</v>
       </c>
@@ -12981,7 +12981,7 @@
       <c r="G215" s="10"/>
       <c r="H215" s="10"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A216" s="1">
         <v>1236967</v>
       </c>
@@ -13008,7 +13008,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A217" s="3" t="s">
         <v>153</v>
       </c>
@@ -13033,7 +13033,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A218" s="20">
         <v>1678861</v>
       </c>
@@ -13056,7 +13056,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A219" s="1">
         <v>1376268</v>
       </c>
@@ -13085,7 +13085,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A220" s="1">
         <v>323873</v>
       </c>
@@ -13105,7 +13105,7 @@
       <c r="G220" s="10"/>
       <c r="H220" s="10"/>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A221" s="1">
         <v>354472</v>
       </c>
@@ -13125,7 +13125,7 @@
       <c r="G221" s="10"/>
       <c r="H221" s="10"/>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A222" s="1">
         <v>329326</v>
       </c>
@@ -13145,7 +13145,7 @@
       <c r="G222" s="10"/>
       <c r="H222" s="10"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A223" s="1">
         <v>541201</v>
       </c>
@@ -13174,7 +13174,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A224" s="1">
         <v>520221</v>
       </c>
@@ -13203,7 +13203,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A225" s="1">
         <v>577478</v>
       </c>
@@ -13223,7 +13223,7 @@
       <c r="G225" s="10"/>
       <c r="H225" s="10"/>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A226" s="1">
         <v>424770</v>
       </c>
@@ -13243,7 +13243,7 @@
       <c r="G226" s="10"/>
       <c r="H226" s="10"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A227" s="1">
         <v>415117</v>
       </c>
@@ -13272,7 +13272,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A228" s="1">
         <v>323865</v>
       </c>
@@ -13292,7 +13292,7 @@
       <c r="G228" s="10"/>
       <c r="H228" s="10"/>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A229" s="1">
         <v>1393578</v>
       </c>
@@ -13312,7 +13312,7 @@
       <c r="G229" s="10"/>
       <c r="H229" s="10"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A230" s="1">
         <v>1376318</v>
       </c>
@@ -13341,7 +13341,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A231" s="1">
         <v>1315084</v>
       </c>
@@ -13370,7 +13370,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A232" s="1">
         <v>414987</v>
       </c>
@@ -13399,7 +13399,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A233" s="1">
         <v>1378702</v>
       </c>
@@ -13419,7 +13419,7 @@
       <c r="G233" s="10"/>
       <c r="H233" s="10"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A234" s="1">
         <v>1376300</v>
       </c>
@@ -13448,7 +13448,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A235" s="1">
         <v>1381862</v>
       </c>
@@ -13468,7 +13468,7 @@
       <c r="G235" s="10"/>
       <c r="H235" s="10"/>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A236" s="1">
         <v>1153162</v>
       </c>
@@ -13488,7 +13488,7 @@
       <c r="G236" s="10"/>
       <c r="H236" s="10"/>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A237" s="1">
         <v>1613371</v>
       </c>
@@ -13508,7 +13508,7 @@
       <c r="G237" s="10"/>
       <c r="H237" s="10"/>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A238" s="1">
         <v>701284</v>
       </c>
@@ -13528,7 +13528,7 @@
       <c r="G238" s="10"/>
       <c r="H238" s="10"/>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A239" s="1">
         <v>1268119</v>
       </c>
@@ -13548,7 +13548,7 @@
       <c r="G239" s="10"/>
       <c r="H239" s="10"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A240" s="26">
         <v>415141</v>
       </c>
@@ -13577,7 +13577,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A241" s="1">
         <v>1608132</v>
       </c>
@@ -13606,7 +13606,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A242" s="1">
         <v>1547231</v>
       </c>
@@ -13626,7 +13626,7 @@
       <c r="G242" s="10"/>
       <c r="H242" s="10"/>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A243" s="1">
         <v>1116896</v>
       </c>
@@ -13646,7 +13646,7 @@
       <c r="G243" s="10"/>
       <c r="H243" s="10"/>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A244" s="1">
         <v>1130012</v>
       </c>
@@ -13666,7 +13666,7 @@
       <c r="G244" s="10"/>
       <c r="H244" s="10"/>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A245" s="1">
         <v>1393594</v>
       </c>
@@ -13686,7 +13686,7 @@
       <c r="G245" s="10"/>
       <c r="H245" s="10"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A246" s="1">
         <v>686386</v>
       </c>
@@ -13715,7 +13715,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A247" s="1">
         <v>415141</v>
       </c>
@@ -13744,7 +13744,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A248" s="1">
         <v>838455</v>
       </c>
@@ -13771,7 +13771,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A249" s="1">
         <v>1551944</v>
       </c>
@@ -13800,7 +13800,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A250" s="1">
         <v>757872</v>
       </c>
@@ -13820,7 +13820,7 @@
       <c r="G250" s="10"/>
       <c r="H250" s="10"/>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A251" s="1">
         <v>1538461</v>
       </c>
@@ -13840,7 +13840,7 @@
       <c r="G251" s="10"/>
       <c r="H251" s="10"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A252" s="1">
         <v>1678879</v>
       </c>
@@ -13869,7 +13869,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A253" s="1">
         <v>818682</v>
       </c>
@@ -13898,7 +13898,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A254" s="1">
         <v>693374</v>
       </c>
@@ -13918,7 +13918,7 @@
       <c r="G254" s="10"/>
       <c r="H254" s="10"/>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A255" s="1">
         <v>578450</v>
       </c>
@@ -13938,7 +13938,7 @@
       <c r="G255" s="10"/>
       <c r="H255" s="10"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A256" s="1">
         <v>415059</v>
       </c>
@@ -13967,7 +13967,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A257" s="1">
         <v>1041631</v>
       </c>
@@ -13987,7 +13987,7 @@
       <c r="G257" s="10"/>
       <c r="H257" s="10"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A258" s="1">
         <v>1633189</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A259" s="1">
         <v>830885</v>
       </c>
@@ -14045,7 +14045,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A260" s="1">
         <v>1370709</v>
       </c>
@@ -14065,7 +14065,7 @@
       <c r="G260" s="10"/>
       <c r="H260" s="10"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A261" s="1">
         <v>1625938</v>
       </c>
@@ -14094,7 +14094,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A262" s="1">
         <v>1186451</v>
       </c>
@@ -14114,7 +14114,7 @@
       <c r="G262" s="10"/>
       <c r="H262" s="10"/>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A263" s="1">
         <v>693382</v>
       </c>
@@ -14134,7 +14134,7 @@
       <c r="G263" s="10"/>
       <c r="H263" s="10"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A264" s="1">
         <v>657122</v>
       </c>
@@ -14163,7 +14163,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A265" s="1">
         <v>595082</v>
       </c>
@@ -14192,7 +14192,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A266" s="1">
         <v>1393602</v>
       </c>
@@ -14212,7 +14212,7 @@
       <c r="G266" s="10"/>
       <c r="H266" s="10"/>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A267" s="1">
         <v>1197987</v>
       </c>
@@ -14232,7 +14232,7 @@
       <c r="G267" s="10"/>
       <c r="H267" s="10"/>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A268" s="1">
         <v>1210137</v>
       </c>
@@ -14252,7 +14252,7 @@
       <c r="G268" s="10"/>
       <c r="H268" s="10"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A269" s="1">
         <v>273359</v>
       </c>
@@ -14281,7 +14281,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A270" s="1">
         <v>1626001</v>
       </c>
@@ -14310,7 +14310,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A271" s="1">
         <v>402248</v>
       </c>
@@ -14330,7 +14330,7 @@
       <c r="G271" s="10"/>
       <c r="H271" s="10"/>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A272" s="1">
         <v>636704</v>
       </c>
@@ -14350,7 +14350,7 @@
       <c r="G272" s="10"/>
       <c r="H272" s="10"/>
     </row>
-    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A273" s="1">
         <v>1257245</v>
       </c>
@@ -14370,7 +14370,7 @@
       <c r="G273" s="10"/>
       <c r="H273" s="10"/>
     </row>
-    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A274" s="1">
         <v>1261189</v>
       </c>
@@ -14390,7 +14390,7 @@
       <c r="G274" s="10"/>
       <c r="H274" s="10"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A275" s="1">
         <v>666677</v>
       </c>
@@ -14419,7 +14419,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A276" s="1">
         <v>1236686</v>
       </c>
@@ -14439,7 +14439,7 @@
       <c r="G276" s="10"/>
       <c r="H276" s="10"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A277" s="1">
         <v>1568799</v>
       </c>
@@ -14468,7 +14468,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A278" s="1">
         <v>272773</v>
       </c>
@@ -14497,7 +14497,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A279" s="1">
         <v>1104801</v>
       </c>
@@ -14517,7 +14517,7 @@
       <c r="G279" s="10"/>
       <c r="H279" s="10"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A280" s="1">
         <v>271551</v>
       </c>
@@ -14546,7 +14546,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A281" s="1">
         <v>1714211</v>
       </c>
@@ -14566,7 +14566,7 @@
       <c r="G281" s="10"/>
       <c r="H281" s="10"/>
     </row>
-    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A282" s="1">
         <v>437517</v>
       </c>
@@ -14586,7 +14586,7 @@
       <c r="G282" s="10"/>
       <c r="H282" s="10"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A283" s="1">
         <v>272567</v>
       </c>
@@ -14612,7 +14612,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A284" s="1">
         <v>1155530</v>
       </c>
@@ -14632,7 +14632,7 @@
       <c r="G284" s="10"/>
       <c r="H284" s="10"/>
     </row>
-    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A285" s="1">
         <v>1265768</v>
       </c>
@@ -14652,7 +14652,7 @@
       <c r="G285" s="10"/>
       <c r="H285" s="10"/>
     </row>
-    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A286" s="1">
         <v>433037</v>
       </c>
@@ -14672,7 +14672,7 @@
       <c r="G286" s="10"/>
       <c r="H286" s="10"/>
     </row>
-    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A287" s="1">
         <v>762880</v>
       </c>
@@ -14692,7 +14692,7 @@
       <c r="G287" s="10"/>
       <c r="H287" s="10"/>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A288" s="1">
         <v>275107</v>
       </c>
@@ -14721,7 +14721,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A289" s="1">
         <v>733535</v>
       </c>
@@ -14750,7 +14750,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A290" s="1">
         <v>1370717</v>
       </c>
@@ -14770,7 +14770,7 @@
       <c r="G290" s="10"/>
       <c r="H290" s="10"/>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A291" s="1">
         <v>761585</v>
       </c>
@@ -14790,7 +14790,7 @@
       <c r="G291" s="10"/>
       <c r="H291" s="10"/>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A292" s="1">
         <v>1276120</v>
       </c>
@@ -14810,7 +14810,7 @@
       <c r="G292" s="10"/>
       <c r="H292" s="10"/>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A293" s="1">
         <v>876441</v>
       </c>
@@ -14830,7 +14830,7 @@
       <c r="G293" s="10"/>
       <c r="H293" s="10"/>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A294" s="1">
         <v>807156</v>
       </c>
@@ -14859,7 +14859,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A295" s="1">
         <v>535195</v>
       </c>
@@ -14879,7 +14879,7 @@
       <c r="G295" s="10"/>
       <c r="H295" s="10"/>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A296" s="1">
         <v>1276674</v>
       </c>
@@ -14899,7 +14899,7 @@
       <c r="G296" s="10"/>
       <c r="H296" s="10"/>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A297" s="1">
         <v>290809</v>
       </c>
@@ -14919,7 +14919,7 @@
       <c r="G297" s="10"/>
       <c r="H297" s="10"/>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A298" s="1">
         <v>1070630</v>
       </c>
@@ -14939,7 +14939,7 @@
       <c r="G298" s="10"/>
       <c r="H298" s="10"/>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A299" s="1">
         <v>334995</v>
       </c>
@@ -14959,7 +14959,7 @@
       <c r="G299" s="10"/>
       <c r="H299" s="10"/>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A300" s="1">
         <v>1625904</v>
       </c>
@@ -14988,7 +14988,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A301" s="1">
         <v>733600</v>
       </c>
@@ -15017,7 +15017,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A302" s="1">
         <v>359042</v>
       </c>
@@ -15037,7 +15037,7 @@
       <c r="G302" s="10"/>
       <c r="H302" s="10"/>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A303" s="1">
         <v>271379</v>
       </c>
@@ -15066,7 +15066,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A304" s="1">
         <v>1324185</v>
       </c>
@@ -15086,7 +15086,7 @@
       <c r="G304" s="10"/>
       <c r="H304" s="10"/>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A305" s="1">
         <v>595108</v>
       </c>
@@ -15115,7 +15115,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A306" s="1">
         <v>530535</v>
       </c>
@@ -15144,7 +15144,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A307" s="1">
         <v>715011</v>
       </c>
@@ -15173,7 +15173,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A308" s="23">
         <v>1433515</v>
       </c>
@@ -15202,7 +15202,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A309" s="23">
         <v>1625987</v>
       </c>
@@ -15231,7 +15231,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A310" s="20">
         <v>740365</v>
       </c>
@@ -15260,7 +15260,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A311" s="1">
         <v>900647</v>
       </c>
@@ -15281,7 +15281,7 @@
       <c r="H311" s="13"/>
       <c r="I311" s="29"/>
     </row>
-    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A312" s="1">
         <v>495234</v>
       </c>
@@ -15302,7 +15302,7 @@
       <c r="H312" s="12"/>
       <c r="I312" s="29"/>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A313" s="1">
         <v>420406</v>
       </c>
@@ -15331,7 +15331,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A314" s="1">
         <v>421594</v>
       </c>
@@ -15360,7 +15360,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A315" s="1">
         <v>686741</v>
       </c>
@@ -15389,7 +15389,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A316" s="1">
         <v>420562</v>
       </c>
@@ -15418,7 +15418,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A317" s="1">
         <v>1393586</v>
       </c>
@@ -15439,7 +15439,7 @@
       <c r="H317" s="13"/>
       <c r="I317" s="29"/>
     </row>
-    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A318" s="1">
         <v>577841</v>
       </c>
@@ -15460,7 +15460,7 @@
       <c r="H318" s="12"/>
       <c r="I318" s="29"/>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A319" s="1">
         <v>687194</v>
       </c>
@@ -15489,7 +15489,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A320" s="1">
         <v>633040</v>
       </c>
@@ -15518,7 +15518,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A321" s="1">
         <v>1396258</v>
       </c>
@@ -15539,7 +15539,7 @@
       <c r="H321" s="14"/>
       <c r="I321" s="29"/>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A322" s="1">
         <v>1374834</v>
       </c>
@@ -15568,7 +15568,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A323" s="1">
         <v>761668</v>
       </c>
@@ -15589,7 +15589,7 @@
       <c r="H323" s="13"/>
       <c r="I323" s="29"/>
     </row>
-    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A324" s="1">
         <v>714410</v>
       </c>
@@ -15610,7 +15610,7 @@
       <c r="H324" s="12"/>
       <c r="I324" s="29"/>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A325" s="1">
         <v>420380</v>
       </c>
@@ -15639,7 +15639,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A326" s="1">
         <v>428920</v>
       </c>
@@ -15668,7 +15668,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A327" s="1">
         <v>600692</v>
       </c>
@@ -15697,7 +15697,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A328" s="1">
         <v>1785138</v>
       </c>
@@ -15726,7 +15726,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A329" s="17">
         <v>1402692</v>
       </c>
@@ -15749,7 +15749,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A330" s="1">
         <v>778076</v>
       </c>
@@ -15769,7 +15769,7 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A331" s="17">
         <v>600932</v>
       </c>
@@ -15792,7 +15792,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A332" s="1">
         <v>1448596</v>
       </c>
@@ -15812,7 +15812,7 @@
       <c r="G332" s="13"/>
       <c r="H332" s="13"/>
     </row>
-    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A333" s="1">
         <v>1364264</v>
       </c>
@@ -15832,7 +15832,7 @@
       <c r="G333" s="10"/>
       <c r="H333" s="10"/>
     </row>
-    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A334" s="1">
         <v>433045</v>
       </c>
@@ -15852,7 +15852,7 @@
       <c r="G334" s="10"/>
       <c r="H334" s="10"/>
     </row>
-    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A335" s="1">
         <v>762500</v>
       </c>
@@ -15872,7 +15872,7 @@
       <c r="G335" s="12"/>
       <c r="H335" s="12"/>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A336" s="1">
         <v>1495167</v>
       </c>
@@ -15901,7 +15901,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A337" s="1">
         <v>428771</v>
       </c>
@@ -15930,7 +15930,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A338" s="1">
         <v>1060276</v>
       </c>
@@ -15959,7 +15959,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A339" s="1">
         <v>1192921</v>
       </c>
@@ -15980,7 +15980,7 @@
       <c r="H339" s="14"/>
       <c r="I339" s="29"/>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A340" s="1">
         <v>579987</v>
       </c>
@@ -16009,7 +16009,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A341" s="1">
         <v>428714</v>
       </c>
@@ -16038,7 +16038,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A342" s="1">
         <v>1367358</v>
       </c>
@@ -16059,7 +16059,7 @@
       <c r="H342" s="14"/>
       <c r="I342" s="29"/>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A343" s="1">
         <v>420430</v>
       </c>
@@ -16088,7 +16088,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A344" s="1">
         <v>843326</v>
       </c>
@@ -16109,7 +16109,7 @@
       <c r="H344" s="13"/>
       <c r="I344" s="29"/>
     </row>
-    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A345" s="1">
         <v>1448588</v>
       </c>
@@ -16130,7 +16130,7 @@
       <c r="H345" s="12"/>
       <c r="I345" s="29"/>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A346" s="1">
         <v>420448</v>
       </c>
@@ -16159,7 +16159,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A347" s="1">
         <v>1329788</v>
       </c>
@@ -16180,7 +16180,7 @@
       <c r="H347" s="14"/>
       <c r="I347" s="29"/>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A348" s="3">
         <v>1402866</v>
       </c>
@@ -16209,178 +16209,178 @@
         <v>123</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B351" s="27"/>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A352" s="27"/>
       <c r="B352" s="27"/>
       <c r="C352" s="27"/>
       <c r="D352" s="27"/>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A353" s="27"/>
       <c r="B353" s="27"/>
       <c r="C353" s="27"/>
       <c r="D353" s="27"/>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A354" s="27"/>
       <c r="B354" s="27"/>
       <c r="C354" s="27"/>
       <c r="D354" s="27"/>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A355" s="27"/>
       <c r="B355" s="27"/>
       <c r="C355" s="27"/>
       <c r="D355" s="27"/>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A356" s="27"/>
       <c r="B356" s="27"/>
       <c r="C356" s="27"/>
       <c r="D356" s="27"/>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A357" s="27"/>
       <c r="B357" s="27"/>
       <c r="C357" s="27"/>
       <c r="D357" s="27"/>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A358" s="27"/>
       <c r="B358" s="27"/>
       <c r="C358" s="27"/>
       <c r="D358" s="27"/>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A359" s="27"/>
       <c r="B359" s="27"/>
       <c r="C359" s="27"/>
       <c r="D359" s="27"/>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A360" s="27"/>
       <c r="B360" s="27"/>
       <c r="C360" s="27"/>
       <c r="D360" s="27"/>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" s="27"/>
       <c r="B361" s="27"/>
       <c r="C361" s="27"/>
       <c r="D361" s="27"/>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A362" s="27"/>
       <c r="B362" s="27"/>
       <c r="C362" s="27"/>
       <c r="D362" s="27"/>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A363" s="27"/>
       <c r="B363" s="27"/>
       <c r="C363" s="27"/>
       <c r="D363" s="27"/>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A364" s="27"/>
       <c r="B364" s="27"/>
       <c r="C364" s="27"/>
       <c r="D364" s="27"/>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A365" s="27"/>
       <c r="B365" s="27"/>
       <c r="C365" s="27"/>
       <c r="D365" s="27"/>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A366" s="27"/>
       <c r="B366" s="27"/>
       <c r="C366" s="27"/>
       <c r="D366" s="27"/>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A367" s="27"/>
       <c r="B367" s="27"/>
       <c r="C367" s="27"/>
       <c r="D367" s="27"/>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A368" s="27"/>
       <c r="B368" s="27"/>
       <c r="C368" s="27"/>
       <c r="D368" s="27"/>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A369" s="27"/>
       <c r="B369" s="27"/>
       <c r="C369" s="27"/>
       <c r="D369" s="27"/>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" s="27"/>
       <c r="B370" s="27"/>
       <c r="C370" s="27"/>
       <c r="D370" s="27"/>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A371" s="27"/>
       <c r="B371" s="27"/>
       <c r="C371" s="27"/>
       <c r="D371" s="27"/>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A372" s="27"/>
       <c r="B372" s="27"/>
       <c r="C372" s="27"/>
       <c r="D372" s="27"/>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A373" s="27"/>
       <c r="B373" s="27"/>
       <c r="C373" s="27"/>
       <c r="D373" s="27"/>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A374" s="27"/>
       <c r="B374" s="27"/>
       <c r="C374" s="27"/>
       <c r="D374" s="27"/>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A375" s="27"/>
       <c r="B375" s="27"/>
       <c r="C375" s="27"/>
       <c r="D375" s="27"/>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A376" s="27"/>
       <c r="B376" s="27"/>
       <c r="C376" s="27"/>
       <c r="D376" s="27"/>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A377" s="27"/>
       <c r="B377" s="27"/>
       <c r="C377" s="27"/>
       <c r="D377" s="27"/>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A378" s="27"/>
       <c r="B378" s="27"/>
       <c r="C378" s="27"/>
       <c r="D378" s="27"/>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" s="27"/>
       <c r="B379" s="27"/>
       <c r="C379" s="27"/>
       <c r="D379" s="27"/>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A380" s="27"/>
       <c r="B380" s="27"/>
       <c r="C380" s="27"/>
